--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484632_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484632_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.148300000000001</v>
+        <v>8.5937</v>
       </c>
       <c r="E2" t="n">
-        <v>6.602</v>
+        <v>5.9979</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5463</v>
+        <v>2.5958</v>
       </c>
       <c r="G2" t="n">
         <v>3.1878</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.205</v>
+        <v>0.6505</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7655</v>
+        <v>0.1614</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4395</v>
+        <v>0.489</v>
       </c>
       <c r="V2" t="n">
         <v>2.7396</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1392</v>
+        <v>1.7819</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7643</v>
+        <v>1.5309</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3749</v>
+        <v>0.251</v>
       </c>
       <c r="G4" t="n">
         <v>1.8009</v>
@@ -766,13 +766,13 @@
         <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6874</v>
+        <v>0.3301</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4563</v>
+        <v>0.2229</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2311</v>
+        <v>0.1073</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0821</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6954</v>
+        <v>1.4372</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1721</v>
+        <v>-0.4055</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8675</v>
+        <v>1.8428</v>
       </c>
       <c r="G5" t="n">
         <v>1.7173</v>
@@ -844,13 +844,13 @@
         <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5883</v>
+        <v>0.3301</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0761</v>
+        <v>-0.3095</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6644</v>
+        <v>0.6397</v>
       </c>
       <c r="V5" t="n">
         <v>1.5889</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1762</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4613</v>
+        <v>0.5714</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3704</v>
+        <v>-0.3952</v>
       </c>
       <c r="G8" t="n">
         <v>0.7304</v>
@@ -1078,13 +1078,13 @@
         <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4051</v>
+        <v>0.4904</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0196</v>
+        <v>0.0905</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4246</v>
+        <v>0.3999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3115</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1802</v>
+        <v>-1.1209</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.778</v>
+        <v>-4.0499</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5978</v>
+        <v>2.9289</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2154</v>
@@ -1156,13 +1156,13 @@
         <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5835</v>
+        <v>0.6427</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.138</v>
+        <v>-0.4099</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7214</v>
+        <v>1.0526</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4486</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8284</v>
+        <v>-2.1248</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2168</v>
+        <v>-2.5875</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3884</v>
+        <v>0.4628</v>
       </c>
       <c r="G10" t="n">
         <v>-2.559</v>
@@ -1234,13 +1234,13 @@
         <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.2102</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2542</v>
+        <v>-0.1165</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2524</v>
+        <v>0.3267</v>
       </c>
       <c r="V10" t="n">
         <v>1.1403</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0258</v>
+        <v>-2.8023</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3148</v>
+        <v>-1.8857</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.711</v>
+        <v>-0.9166</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5269</v>
+        <v>-2.3902</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2189</v>
+        <v>-1.0404</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.308</v>
+        <v>-1.3498</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1119</v>
+        <v>-1.312</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1701</v>
+        <v>-0.796</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2821</v>
+        <v>-0.516</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4149</v>
+        <v>-1.0781</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.389</v>
+        <v>-0.2443</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0259</v>
+        <v>-0.8338</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1346</v>
+        <v>-0.0002</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0196</v>
+        <v>-0.2726</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1541</v>
+        <v>0.2724</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.6948</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7531</v>
+        <v>-3.093</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8612</v>
+        <v>-3.3807</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8918</v>
+        <v>0.2877</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3902</v>
+        <v>-2.0964</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0404</v>
+        <v>-0.2439</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3498</v>
+        <v>-1.8525</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.312</v>
+        <v>-1.78</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.796</v>
+        <v>0.0401</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.516</v>
+        <v>-1.82</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0781</v>
+        <v>-0.3164</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2443</v>
+        <v>-0.284</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8338</v>
+        <v>-0.0324</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9509</v>
+        <v>-0.2794</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2481</v>
+        <v>-0.3729</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2972</v>
+        <v>0.0935</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6948</v>
+        <v>-1.267</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3011</v>
+        <v>-0.3115</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3937</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4157</v>
+        <v>-3.1517</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1088</v>
+        <v>-1.5893</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3069</v>
+        <v>-1.5624</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0964</v>
+        <v>-3.5269</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2439</v>
+        <v>-1.2189</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8525</v>
+        <v>-2.308</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.78</v>
+        <v>-1.1119</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0401</v>
+        <v>0.1701</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.82</v>
+        <v>-1.2821</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3164</v>
+        <v>-2.4149</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.284</v>
+        <v>-1.389</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0324</v>
+        <v>-1.0259</v>
       </c>
       <c r="P13" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.1833</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.5498</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-0.9163</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4661</v>
-      </c>
       <c r="S13" t="n">
-        <v>-1.6021</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.101</v>
+        <v>-0.2941</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5011</v>
+        <v>0.3028</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.671500000000001</v>
+        <v>3.497199999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.8232</v>
+        <v>-1.9975</v>
       </c>
       <c r="F14" t="n">
-        <v>5.494800000000001</v>
+        <v>5.4948</v>
       </c>
       <c r="G14" t="n">
-        <v>0.449399999999998</v>
+        <v>0.4493999999999976</v>
       </c>
       <c r="H14" t="n">
         <v>8.623699999999999</v>
@@ -1519,13 +1519,13 @@
         <v>-8.174199999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7729</v>
+        <v>5.772900000000001</v>
       </c>
       <c r="K14" t="n">
         <v>11.8604</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.087700000000001</v>
+        <v>-6.0877</v>
       </c>
       <c r="M14" t="n">
         <v>-5.323399999999999</v>
@@ -1537,7 +1537,7 @@
         <v>-2.0867</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>-1.665334536937735e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.9118</v>
@@ -1546,13 +1546,13 @@
         <v>11.9117</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5575</v>
+        <v>2.3831</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1264</v>
+        <v>-1.3007</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6836</v>
+        <v>3.6839</v>
       </c>
       <c r="V14" t="n">
         <v>0.6647999999999998</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. ORSINO BARCIA</t>
+          <t>P. ARISTA CALLAU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.803</v>
+        <v>4.2882</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3542</v>
+        <v>3.264</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4488</v>
+        <v>1.0242</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1272</v>
+        <v>4.1919</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6267</v>
+        <v>-1.6358</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5005</v>
+        <v>5.8277</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8693</v>
+        <v>3.5713</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4584</v>
+        <v>-1.0068</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4109</v>
+        <v>4.5781</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7421</v>
+        <v>0.6207</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8317</v>
+        <v>-0.629</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0896</v>
+        <v>1.2496</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="R15" t="n">
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2202</v>
+        <v>-0.3986</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3318</v>
+        <v>-0.4747</v>
       </c>
       <c r="U15" t="n">
-        <v>0.552</v>
+        <v>0.0761</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6439</v>
+        <v>0.3115</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6439</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ARISTA CALLAU</t>
+          <t>L. ORSINO BARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7665</v>
+        <v>3.6835</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1678</v>
+        <v>3.3542</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5987</v>
+        <v>0.3293</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1919</v>
+        <v>3.1272</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6358</v>
+        <v>0.6267</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8277</v>
+        <v>2.5005</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5713</v>
+        <v>3.8693</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0068</v>
+        <v>2.4584</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5781</v>
+        <v>1.4109</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6207</v>
+        <v>-0.7421</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.629</v>
+        <v>-1.8317</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2496</v>
+        <v>1.0896</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R16" t="n">
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9202</v>
+        <v>0.1007</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5709</v>
+        <v>-0.3318</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3493</v>
+        <v>0.4325</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3115</v>
+        <v>-0.6439</v>
       </c>
       <c r="W16" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9554</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4406</v>
+        <v>1.8849</v>
       </c>
       <c r="E17" t="n">
-        <v>1.125</v>
+        <v>1.3173</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3156</v>
+        <v>0.5677</v>
       </c>
       <c r="G17" t="n">
         <v>0.1831</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6142</v>
+        <v>-0.1699</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5784</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1565</v>
+        <v>0.4085</v>
       </c>
       <c r="V17" t="n">
         <v>0.9554</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2933</v>
+        <v>0.6269</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1475</v>
+        <v>-0.0809</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1459</v>
+        <v>0.7079</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7359</v>
+        <v>1.1871</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.1244</v>
+        <v>0.623</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3885</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.5477</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1645</v>
+        <v>1.1054</v>
       </c>
       <c r="L19" t="n">
-        <v>2.036</v>
+        <v>-0.5577</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6074</v>
+        <v>0.6394</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9599</v>
+        <v>-0.4824</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3525</v>
+        <v>1.1217</v>
       </c>
       <c r="P19" t="n">
         <v>0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9847</v>
+        <v>-0.2932</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1297</v>
+        <v>-0.3171</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1144</v>
+        <v>0.0239</v>
       </c>
       <c r="V19" t="n">
+        <v>-0.6335</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.3115</v>
+      </c>
+      <c r="X19" t="n">
         <v>-0.3219</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.3219</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.6439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>D. IGUAL BAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0864</v>
+        <v>-0.042</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3694</v>
+        <v>-0.0668</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4558</v>
+        <v>0.0248</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1871</v>
+        <v>-0.4223</v>
       </c>
       <c r="H20" t="n">
-        <v>0.623</v>
+        <v>-0.0055</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5639999999999999</v>
+        <v>-0.4167</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5477</v>
+        <v>0.0433</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1054</v>
+        <v>0.0433</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5577</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6394</v>
+        <v>-0.4656</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4824</v>
+        <v>-0.0489</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1217</v>
+        <v>-0.4167</v>
       </c>
       <c r="P20" t="n">
         <v>0.3665</v>
@@ -2014,28 +2014,28 @@
         <v>0.3665</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8337</v>
+        <v>0.0138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6056</v>
+        <v>-0.1101</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2281</v>
+        <v>0.1239</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. IGUAL BAU</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1163</v>
+        <v>-0.1458</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0668</v>
+        <v>-0.5513</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0496</v>
+        <v>0.4055</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4223</v>
+        <v>0.3493</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0055</v>
+        <v>-0.1282</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4167</v>
+        <v>0.4775</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0433</v>
+        <v>0.5769</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0433</v>
+        <v>1.0929</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.516</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4656</v>
+        <v>-0.2276</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0489</v>
+        <v>-1.2211</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4167</v>
+        <v>0.9935</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3665</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
         <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0606</v>
+        <v>0.0547</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1101</v>
+        <v>-0.2119</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0495</v>
+        <v>0.2666</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2012</v>
+        <v>-0.1919</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.359</v>
+        <v>-0.0449</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1578</v>
+        <v>-0.1471</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3493</v>
+        <v>-0.7359</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1282</v>
+        <v>-3.1244</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4775</v>
+        <v>2.3885</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5769</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0929</v>
+        <v>-1.1645</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.516</v>
+        <v>2.036</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2276</v>
+        <v>-1.6074</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2211</v>
+        <v>-1.9599</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9935</v>
+        <v>0.3525</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0007</v>
+        <v>0.4994</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0196</v>
+        <v>-0.322</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0188</v>
+        <v>0.8214</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3604</v>
+        <v>-0.2555</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9839</v>
+        <v>-1.1762</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.9208</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7149</v>
@@ -2248,13 +2248,13 @@
         <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5356</v>
+        <v>-0.4306</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0898</v>
+        <v>-0.1025</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6254</v>
+        <v>-0.3281</v>
       </c>
       <c r="V23" t="n">
         <v>1.2566</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0031</v>
+        <v>-1.904</v>
       </c>
       <c r="E24" t="n">
         <v>-1.719</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2841</v>
+        <v>-0.185</v>
       </c>
       <c r="G24" t="n">
         <v>-0.582</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2824</v>
+        <v>-0.1833</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2941</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0118</v>
+        <v>0.1108</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9554</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9216</v>
+        <v>-3.2348</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7088</v>
+        <v>-3.9972</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7872</v>
+        <v>0.7624</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9441</v>
@@ -2404,13 +2404,13 @@
         <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1117</v>
+        <v>-0.2015</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.095</v>
+        <v>-0.3834</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2067</v>
+        <v>0.1819</v>
       </c>
       <c r="V25" t="n">
         <v>0.6439</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.4913</v>
+        <v>-3.3791</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.6098</v>
+        <v>-4.2251</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1185</v>
+        <v>0.846</v>
       </c>
       <c r="G26" t="n">
         <v>-3.0909</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3453</v>
+        <v>-0.2332</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0467</v>
+        <v>-0.6621</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7014</v>
+        <v>0.4289</v>
       </c>
       <c r="V26" t="n">
         <v>0.3115</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.6178</v>
+        <v>-4.0112</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.1229</v>
+        <v>-2.2191</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4948</v>
+        <v>-1.7921</v>
       </c>
       <c r="G27" t="n">
         <v>-1.6481</v>
@@ -2560,13 +2560,13 @@
         <v>0.733</v>
       </c>
       <c r="S27" t="n">
-        <v>0.7188</v>
+        <v>0.3254</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2006</v>
+        <v>0.1045</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5182</v>
+        <v>0.221</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5889</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.6717</v>
+        <v>-2.0306</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.494900000000001</v>
+        <v>-5.494800000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8233</v>
+        <v>3.4644</v>
       </c>
       <c r="G28" t="n">
         <v>-0.4493999999999998</v>
@@ -2611,7 +2611,7 @@
         <v>8.174200000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>5.323500000000003</v>
+        <v>5.323500000000001</v>
       </c>
       <c r="K28" t="n">
         <v>3.2367</v>
@@ -2638,13 +2638,13 @@
         <v>11.9116</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.5573</v>
+        <v>-0.9163</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.6838</v>
+        <v>-3.6836</v>
       </c>
       <c r="U28" t="n">
-        <v>2.1265</v>
+        <v>2.7674</v>
       </c>
       <c r="V28" t="n">
         <v>-0.6647000000000001</v>
